--- a/education_forms/044_emergency_contact_sheet--education_forms.xlsx
+++ b/education_forms/044_emergency_contact_sheet--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,8 +853,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -882,12 +882,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'parent/guardian'}</t>
+          <t>parent/guardian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Parent/Guardian'}</t>
+          <t>Parent/Guardian</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'spouse/elder'}</t>
+          <t>spouse/elder</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse/Elder'}</t>
+          <t>Spouse/Elder</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'sibling'}</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Sibling'}</t>
+          <t>Sibling</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
